--- a/excel_db/asset_movements.xlsx
+++ b/excel_db/asset_movements.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>id</t>
   </si>
@@ -35,6 +35,18 @@
   </si>
   <si>
     <t>created_at</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>2026-06-07 02:30:17</t>
   </si>
 </sst>
 </file>
@@ -392,10 +404,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -416,6 +428,29 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
